--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/Python worksheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A38E823-87CE-46E5-8F8C-9432391F67D9}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A84B9C3-F8E5-4793-86B6-684F1D4BB369}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,15 @@
   </si>
   <si>
     <t>Energy was lit bit low.</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Regained my energy.</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1089,7 @@
         <v>58</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>57</v>
@@ -1090,26 +1099,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B8" s="14">
+        <v>540</v>
+      </c>
+      <c r="C8" s="14">
+        <v>150</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>150</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>200</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/Python worksheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A84B9C3-F8E5-4793-86B6-684F1D4BB369}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C5C55F4-6DA2-4533-82EE-F0EA80DD34A9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Regained my energy.</t>
+  </si>
+  <si>
+    <t>Solved some important questions.</t>
   </si>
 </sst>
 </file>
@@ -1144,27 +1147,51 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B9" s="14">
+        <v>600</v>
+      </c>
+      <c r="C9" s="14">
+        <v>150</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>180</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>150</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/Python worksheet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C5C55F4-6DA2-4533-82EE-F0EA80DD34A9}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FEA1FFC-EE54-4BAE-AF05-9FC0F8E72275}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>Solved some important questions.</t>
+  </si>
+  <si>
+    <t>Very Satisfies</t>
+  </si>
+  <si>
+    <t>Felt nice.</t>
   </si>
 </sst>
 </file>
@@ -507,10 +513,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1194,26 +1196,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>120</v>
+      </c>
+      <c r="D10" s="14">
+        <v>60</v>
+      </c>
+      <c r="E10" s="14">
+        <v>120</v>
+      </c>
+      <c r="F10" s="14">
+        <v>400</v>
+      </c>
+      <c r="G10" s="14">
+        <v>8</v>
+      </c>
+      <c r="H10" s="14">
+        <v>140</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FEA1FFC-EE54-4BAE-AF05-9FC0F8E72275}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63A83D97-1EAC-40A5-B933-F19EEE553A12}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,10 +229,16 @@
     <t>Solved some important questions.</t>
   </si>
   <si>
-    <t>Very Satisfies</t>
+    <t>Felt nice.</t>
   </si>
   <si>
-    <t>Felt nice.</t>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>Overall day was productive.</t>
   </si>
 </sst>
 </file>
@@ -513,6 +519,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1232,36 +1242,60 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B11" s="14">
+        <v>500</v>
+      </c>
+      <c r="C11" s="14">
+        <v>150</v>
+      </c>
+      <c r="D11" s="14">
+        <v>90</v>
+      </c>
+      <c r="E11" s="14">
+        <v>150</v>
+      </c>
+      <c r="F11" s="14">
+        <v>240</v>
+      </c>
+      <c r="G11" s="14">
+        <v>4</v>
+      </c>
+      <c r="H11" s="14">
+        <v>180</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63A83D97-1EAC-40A5-B933-F19EEE553A12}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48BA827A-5920-4224-9CB3-8CE2E112F209}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>Overall day was productive.</t>
+  </si>
+  <si>
+    <t>Best</t>
+  </si>
+  <si>
+    <t>Felt tired after classes</t>
   </si>
 </sst>
 </file>
@@ -1298,26 +1304,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
+      <c r="C12" s="14">
+        <v>120</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>140</v>
+      </c>
+      <c r="F12" s="14">
+        <v>350</v>
+      </c>
+      <c r="G12" s="14">
+        <v>7</v>
+      </c>
+      <c r="H12" s="14">
+        <v>200</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
@@ -1328,14 +1358,8 @@
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48BA827A-5920-4224-9CB3-8CE2E112F209}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0777521A-3FED-4857-BD01-FA45952B5E80}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>Felt tired after classes</t>
+  </si>
+  <si>
+    <t>Tried solving different dsa problems</t>
   </si>
 </sst>
 </file>
@@ -1349,21 +1352,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B13" s="14">
+        <v>450</v>
+      </c>
+      <c r="C13" s="14">
+        <v>120</v>
+      </c>
+      <c r="D13" s="14">
+        <v>90</v>
+      </c>
+      <c r="E13" s="14">
+        <v>180</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>180</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0777521A-3FED-4857-BD01-FA45952B5E80}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDDF130A-D9A5-48CF-9214-1F1FD6E78F82}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,15 @@
   </si>
   <si>
     <t>Tried solving different dsa problems</t>
+  </si>
+  <si>
+    <t>Productive</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>Solved some important questions and enjoyed playing football.</t>
   </si>
 </sst>
 </file>
@@ -1398,27 +1407,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B14" s="14">
+        <v>600</v>
+      </c>
+      <c r="C14" s="14">
+        <v>150</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>180</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>180</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDDF130A-D9A5-48CF-9214-1F1FD6E78F82}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB1EA7A-012F-409C-8178-BCB164322200}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Solved some important questions and enjoyed playing football.</t>
+  </si>
+  <si>
+    <t>Slept a little bit more and spent time with friends.</t>
   </si>
 </sst>
 </file>
@@ -1453,27 +1456,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B15" s="14">
+        <v>620</v>
+      </c>
+      <c r="C15" s="14">
+        <v>160</v>
+      </c>
+      <c r="D15" s="14">
+        <v>100</v>
+      </c>
+      <c r="E15" s="14">
+        <v>200</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>150</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB1EA7A-012F-409C-8178-BCB164322200}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC10670-0BE2-40DB-A9FC-79FA979A4DBD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Slept a little bit more and spent time with friends.</t>
+  </si>
+  <si>
+    <t>Attended classes and went to play football tournament.</t>
   </si>
 </sst>
 </file>
@@ -1502,27 +1505,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B16" s="14">
+        <v>450</v>
+      </c>
+      <c r="C16" s="14">
+        <v>150</v>
+      </c>
+      <c r="D16" s="14">
+        <v>90</v>
+      </c>
+      <c r="E16" s="14">
+        <v>180</v>
+      </c>
+      <c r="F16" s="14">
+        <v>150</v>
+      </c>
+      <c r="G16" s="14">
+        <v>3</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC10670-0BE2-40DB-A9FC-79FA979A4DBD}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EAEEE83-AF70-4C75-815F-5499F5C6BE12}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>Attended classes and went to play football tournament.</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1552,25 +1555,47 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>120</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>90</v>
+      </c>
+      <c r="F17" s="14">
+        <v>350</v>
+      </c>
+      <c r="G17" s="14">
+        <v>7</v>
+      </c>
+      <c r="H17" s="14">
+        <v>130</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>150</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EAEEE83-AF70-4C75-815F-5499F5C6BE12}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{702A1D68-62F6-4594-8BA6-31E974B0B577}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,18 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Tried solving different dsa problems but got stuck on those problems.</t>
+  </si>
+  <si>
+    <t>Nothing new happened.</t>
+  </si>
+  <si>
+    <t>Light issues</t>
+  </si>
+  <si>
+    <t>Productive day.</t>
   </si>
 </sst>
 </file>
@@ -1554,7 +1566,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>46259</v>
       </c>
@@ -1596,73 +1608,147 @@
       <c r="M17" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B18" s="14">
+        <v>450</v>
+      </c>
+      <c r="C18" s="14">
+        <v>120</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>140</v>
+      </c>
+      <c r="F18" s="14">
+        <v>200</v>
+      </c>
+      <c r="G18" s="14">
+        <v>4</v>
+      </c>
+      <c r="H18" s="14">
+        <v>160</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14">
+        <v>130</v>
+      </c>
+      <c r="D19" s="14">
+        <v>60</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>120</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>160</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>180</v>
+      </c>
+      <c r="F20" s="14">
+        <v>100</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="14">
+        <v>150</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{702A1D68-62F6-4594-8BA6-31E974B0B577}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF2E7436-81FC-4BE0-8C59-5BA3F105E4E6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>Productive day.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Stayed inside the room for whole day.</t>
   </si>
 </sst>
 </file>
@@ -1750,30 +1756,56 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B21" s="14">
+        <v>540</v>
+      </c>
+      <c r="C21" s="14">
+        <v>120</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>120</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="13">
+        <v>46264</v>
+      </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF2E7436-81FC-4BE0-8C59-5BA3F105E4E6}"/>
+  <xr:revisionPtr revIDLastSave="252" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1DC64EF-F2DE-488E-91CD-3FA7419B91CA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>Stayed inside the room for whole day.</t>
+  </si>
+  <si>
+    <t>Went out with friends to enjoy Sunday.</t>
   </si>
 </sst>
 </file>
@@ -1802,29 +1805,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>46264</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="B22" s="14">
+        <v>600</v>
+      </c>
+      <c r="C22" s="14">
+        <v>180</v>
+      </c>
+      <c r="D22" s="14">
+        <v>90</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>240</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="252" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1DC64EF-F2DE-488E-91CD-3FA7419B91CA}"/>
+  <xr:revisionPtr revIDLastSave="264" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB6AAD9B-6DE9-46A1-BC40-CE0FA25C0B68}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Went out with friends to enjoy Sunday.</t>
+  </si>
+  <si>
+    <t>Preprations for upcoming CA.</t>
   </si>
 </sst>
 </file>
@@ -1852,26 +1855,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>120</v>
+      </c>
+      <c r="D23" s="14">
+        <v>60</v>
+      </c>
+      <c r="E23" s="14">
+        <v>240</v>
+      </c>
+      <c r="F23" s="14">
+        <v>150</v>
+      </c>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="264" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB6AAD9B-6DE9-46A1-BC40-CE0FA25C0B68}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{836B1140-D352-4398-9569-F071E582E53B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,12 @@
   </si>
   <si>
     <t>Preprations for upcoming CA.</t>
+  </si>
+  <si>
+    <t>Got very exhausted.</t>
+  </si>
+  <si>
+    <t>Went to play football tournamet after completing classes and enjoyed playing there.</t>
   </si>
 </sst>
 </file>
@@ -1901,48 +1907,96 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B24" s="14">
+        <v>400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>120</v>
+      </c>
+      <c r="D24" s="14">
+        <v>30</v>
+      </c>
+      <c r="E24" s="14">
+        <v>140</v>
+      </c>
+      <c r="F24" s="14">
+        <v>350</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7</v>
+      </c>
+      <c r="H24" s="14">
+        <v>135</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+        <v>265</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B25" s="14">
+        <v>430</v>
+      </c>
+      <c r="C25" s="14">
+        <v>130</v>
+      </c>
+      <c r="D25" s="14">
+        <v>50</v>
+      </c>
+      <c r="E25" s="14">
+        <v>120</v>
+      </c>
+      <c r="F25" s="14">
+        <v>200</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14">
+        <v>110</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="288" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{836B1140-D352-4398-9569-F071E582E53B}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{760AF24A-595D-472C-8F34-A9CD6477D319}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>Went to play football tournamet after completing classes and enjoyed playing there.</t>
+  </si>
+  <si>
+    <t>Gave my PEL CA and it went very well.</t>
   </si>
 </sst>
 </file>
@@ -1998,27 +2001,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B26" s="14">
+        <v>480</v>
+      </c>
+      <c r="C26" s="14">
+        <v>120</v>
+      </c>
+      <c r="D26" s="14">
+        <v>40</v>
+      </c>
+      <c r="E26" s="14">
+        <v>130</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>150</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
